--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -3148,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122325147</v>
+        <v>122325230</v>
       </c>
       <c r="B23" t="n">
-        <v>57390</v>
+        <v>56584</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,50 +3160,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486130</v>
+        <v>486076</v>
       </c>
       <c r="R23" t="n">
-        <v>6566205</v>
+        <v>6566257</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3232,7 +3223,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3242,7 +3233,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flög upp från gammal tall när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3269,10 +3265,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122325230</v>
+        <v>122325147</v>
       </c>
       <c r="B24" t="n">
-        <v>56584</v>
+        <v>57390</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3281,41 +3277,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486076</v>
+        <v>486130</v>
       </c>
       <c r="R24" t="n">
-        <v>6566257</v>
+        <v>6566205</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3344,7 +3349,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3354,12 +3359,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Flög upp från gammal tall när jag gick förbi.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -3148,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122325230</v>
+        <v>122325147</v>
       </c>
       <c r="B23" t="n">
-        <v>56584</v>
+        <v>57395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,41 +3160,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486076</v>
+        <v>486130</v>
       </c>
       <c r="R23" t="n">
-        <v>6566257</v>
+        <v>6566205</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3223,7 +3232,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3233,12 +3242,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flög upp från gammal tall när jag gick förbi.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3265,10 +3269,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122325147</v>
+        <v>122325230</v>
       </c>
       <c r="B24" t="n">
-        <v>57390</v>
+        <v>56589</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3277,50 +3281,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486130</v>
+        <v>486076</v>
       </c>
       <c r="R24" t="n">
-        <v>6566205</v>
+        <v>6566257</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3349,7 +3344,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3359,7 +3354,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flög upp från gammal tall när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -3148,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122325147</v>
+        <v>122325230</v>
       </c>
       <c r="B23" t="n">
-        <v>57395</v>
+        <v>56589</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,50 +3160,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486130</v>
+        <v>486076</v>
       </c>
       <c r="R23" t="n">
-        <v>6566205</v>
+        <v>6566257</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3232,7 +3223,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3242,7 +3233,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flög upp från gammal tall när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3269,10 +3265,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122325230</v>
+        <v>122325147</v>
       </c>
       <c r="B24" t="n">
-        <v>56589</v>
+        <v>57395</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3281,41 +3277,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486076</v>
+        <v>486130</v>
       </c>
       <c r="R24" t="n">
-        <v>6566257</v>
+        <v>6566205</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3344,7 +3349,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3354,12 +3359,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Flög upp från gammal tall när jag gick förbi.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -3148,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122325230</v>
+        <v>122325147</v>
       </c>
       <c r="B23" t="n">
-        <v>56589</v>
+        <v>57395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,41 +3160,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486076</v>
+        <v>486130</v>
       </c>
       <c r="R23" t="n">
-        <v>6566257</v>
+        <v>6566205</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3223,7 +3227,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3233,12 +3237,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flög upp från gammal tall när jag gick förbi.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3265,10 +3264,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122325147</v>
+        <v>122325230</v>
       </c>
       <c r="B24" t="n">
-        <v>57395</v>
+        <v>56589</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3277,50 +3276,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486130</v>
+        <v>486076</v>
       </c>
       <c r="R24" t="n">
-        <v>6566205</v>
+        <v>6566257</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3349,7 +3334,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3359,7 +3344,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flög upp från gammal tall när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>122325147</v>
       </c>
       <c r="B23" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,6 +3165,11 @@
       </c>
       <c r="E23" t="n">
         <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3267,7 +3272,7 @@
         <v>122325230</v>
       </c>
       <c r="B24" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3281,6 +3286,11 @@
       </c>
       <c r="E24" t="n">
         <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>

--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -3148,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122325147</v>
+        <v>122325230</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>56593</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,50 +3160,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486130</v>
+        <v>486076</v>
       </c>
       <c r="R23" t="n">
-        <v>6566205</v>
+        <v>6566257</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3232,7 +3223,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3242,7 +3233,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flög upp från gammal tall när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3269,10 +3265,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122325230</v>
+        <v>122325147</v>
       </c>
       <c r="B24" t="n">
-        <v>56593</v>
+        <v>57399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3281,41 +3277,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486076</v>
+        <v>486130</v>
       </c>
       <c r="R24" t="n">
-        <v>6566257</v>
+        <v>6566205</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3344,7 +3349,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3354,12 +3359,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Flög upp från gammal tall när jag gick förbi.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -3148,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122325230</v>
+        <v>122325147</v>
       </c>
       <c r="B23" t="n">
-        <v>56593</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,41 +3160,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486076</v>
+        <v>486130</v>
       </c>
       <c r="R23" t="n">
-        <v>6566257</v>
+        <v>6566205</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3223,7 +3232,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3233,12 +3242,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flög upp från gammal tall när jag gick förbi.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3265,10 +3269,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122325147</v>
+        <v>122325230</v>
       </c>
       <c r="B24" t="n">
-        <v>57399</v>
+        <v>56593</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3277,50 +3281,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486130</v>
+        <v>486076</v>
       </c>
       <c r="R24" t="n">
-        <v>6566205</v>
+        <v>6566257</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3349,7 +3344,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3359,7 +3354,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flög upp från gammal tall när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>122325147</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>122325230</v>
       </c>
       <c r="B24" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 26878-2020 artfynd.xlsx
+++ b/artfynd/A 26878-2020 artfynd.xlsx
@@ -3148,10 +3148,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122325147</v>
+        <v>122325230</v>
       </c>
       <c r="B23" t="n">
-        <v>57400</v>
+        <v>56594</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3160,50 +3160,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486130</v>
+        <v>486076</v>
       </c>
       <c r="R23" t="n">
-        <v>6566205</v>
+        <v>6566257</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3232,7 +3223,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3242,7 +3233,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flög upp från gammal tall när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3269,10 +3265,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122325230</v>
+        <v>122325147</v>
       </c>
       <c r="B24" t="n">
-        <v>56594</v>
+        <v>57400</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3281,41 +3277,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dorvestorp, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486076</v>
+        <v>486130</v>
       </c>
       <c r="R24" t="n">
-        <v>6566257</v>
+        <v>6566205</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3344,7 +3349,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3354,12 +3359,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Flög upp från gammal tall när jag gick förbi.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
